--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/3642-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/3642-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA880AC4-E097-4389-9CBB-A5F92CFB39CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18B08DA3-C58A-4596-90A8-F4321100A66D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{1040A42F-3FDE-4D2F-A7A3-1BD78B694E11}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{72F03047-6DD4-4E22-AABE-C0BD8E66B89E}"/>
   </bookViews>
   <sheets>
     <sheet name="3642-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1250,19 +1250,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5BBBE8-9D18-4640-8022-4B32D955AEBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E6A75D-F815-4E94-8CAE-75E1182578B9}">
   <dimension ref="A1:Q19"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="9" width="11.77734375" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" customWidth="1"/>
-    <col min="11" max="13" width="11.77734375" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" customWidth="1"/>
-    <col min="15" max="16" width="11.77734375" customWidth="1"/>
-    <col min="17" max="17" width="12.5546875" customWidth="1"/>
+    <col min="1" max="13" width="8.6328125" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" customWidth="1"/>
+    <col min="15" max="16" width="8.6328125" customWidth="1"/>
+    <col min="17" max="17" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1293,7 +1291,7 @@
       <c r="P1" s="17"/>
       <c r="Q1" s="18"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="14"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1344,7 +1342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="15"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1381,7 +1379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>19</v>
       </c>
@@ -1434,7 +1432,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="10">
         <v>2021</v>
       </c>
@@ -1487,7 +1485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2020</v>
       </c>
@@ -1540,7 +1538,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="10">
         <v>2019</v>
       </c>
@@ -1593,7 +1591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2018</v>
       </c>
@@ -1646,7 +1644,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="10">
         <v>2017</v>
       </c>
@@ -1699,7 +1697,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2016</v>
       </c>
@@ -1752,7 +1750,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>2015</v>
       </c>
@@ -1805,7 +1803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>2014</v>
       </c>
@@ -1858,7 +1856,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A13" s="10">
         <v>2013</v>
       </c>
@@ -1911,7 +1909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>2012</v>
       </c>
@@ -1964,7 +1962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A15" s="10">
         <v>2011</v>
       </c>
@@ -2017,7 +2015,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>2010</v>
       </c>
@@ -2070,7 +2068,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A17" s="10">
         <v>2009</v>
       </c>
@@ -2123,7 +2121,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>2008</v>
       </c>
@@ -2176,7 +2174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A19" s="10">
         <v>2007</v>
       </c>
